--- a/business_forms/043_website_handover_confirmation_form--business_forms.xlsx
+++ b/business_forms/043_website_handover_confirmation_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -528,10 +528,14 @@
           <t>Website Details</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Enter website name, URL and description.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -551,7 +555,11 @@
           <t>Client Info</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Client's Name and Email</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -574,7 +582,11 @@
           <t>Transfer Details</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Specify transfer method and date.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -597,7 +609,11 @@
           <t>Confirm Transfer</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Confirm or deny transfer.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>yes</t>
@@ -620,10 +636,14 @@
           <t>Transfer Date</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Enter transfer date.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -643,7 +663,11 @@
           <t>Transfer Time</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Enter transfer time.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>yes</t>
@@ -666,7 +690,11 @@
           <t>Transfer Notes</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Add notes for transfer.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -676,7 +704,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,13 +714,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Client Notes</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Client Confirmations</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Check confirmations</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -709,10 +741,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Client Confirmations</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Confirmations</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Finalize confirmations.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>yes</t>
@@ -732,10 +768,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Confirmations</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Finalize Confirmations</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Finalize confirmations.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>yes</t>
@@ -745,7 +785,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -755,13 +795,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Finalize Transfer</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Client Notes</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Client notes</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -778,310 +822,15 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Confirmations</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Page 12</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Confirm or deny finalize confirmations.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>page_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Finalize Confirmations</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>page_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Finalize Confirmations</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>page_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Finalize Confirmations</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>page_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Finalize Confirmations</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>page_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Finalize Confirmations</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>page_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Finalize Confirmations</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>page_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Finalize Confirmations</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>page_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Finalize Confirmations</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>page_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Finalize Confirmations</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>page_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Finalize Confirmations</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>page_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Finalize Confirmations</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>page_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Finalize Confirmations</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>page_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Finalize Confirmations</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1098,12 +847,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +880,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>client_1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Client 1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +897,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>client_2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Client 2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1165,12 +914,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>client_3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Client 3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1211,119 +960,119 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>page_9_choices</t>
+          <t>page_8_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>confirm</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>page_9_choices</t>
+          <t>page_8_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_confirm</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Not Confirm</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>page_10_choices</t>
+          <t>page_8_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>confirm</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>page_10_choices</t>
+          <t>page_9_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_confirm</t>
+          <t>confirm</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Not Confirm</t>
+          <t>Confirm</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>page_11_choices</t>
+          <t>page_9_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>finalize</t>
+          <t>not_confirm</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Finalize</t>
+          <t>Not Confirm</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>page_11_choices</t>
+          <t>page_10_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_finalize</t>
+          <t>confirm</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Not Finalize</t>
+          <t>Confirm</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>page_12_choices</t>
+          <t>page_10_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>confirm</t>
+          <t>not_confirm</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Not Confirm</t>
         </is>
       </c>
     </row>
@@ -1335,452 +1084,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_confirm</t>
+          <t>confirm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Not Confirm</t>
+          <t>Confirm</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>page_13_choices</t>
+          <t>page_12_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>confirm</t>
+          <t>not_confirm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
-        <is>
-          <t>Confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>page_13_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>not_confirm</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Not Confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>page_14_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>confirm</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>page_14_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>not_confirm</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Not Confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>page_15_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>confirm</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>page_15_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>not_confirm</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Not Confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>page_16_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>confirm</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>page_16_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>not_confirm</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Not Confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>page_17_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>confirm</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>page_17_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>not_confirm</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Not Confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>page_18_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>confirm</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>page_18_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>not_confirm</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Not Confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>page_19_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>confirm</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>page_19_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>not_confirm</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Not Confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>page_20_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>confirm</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>page_20_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>not_confirm</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Not Confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>page_21_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>confirm</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>page_21_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>not_confirm</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Not Confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>page_22_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>confirm</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>page_22_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>not_confirm</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Not Confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>page_23_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>confirm</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>page_23_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>not_confirm</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Not Confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>page_24_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>confirm</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>page_24_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>not_confirm</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Not Confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>page_25_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>confirm</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>page_25_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>not_confirm</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
         <is>
           <t>Not Confirm</t>
         </is>
